--- a/data/trans_orig/P2B_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26839</t>
+          <t>26875</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>36211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51943</t>
+          <t>51951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29984</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>24289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46928</t>
+          <t>46920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62425</t>
+          <t>62660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>27605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43312</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40312</t>
+          <t>40581</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52298</t>
+          <t>52668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45567</t>
+          <t>45611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55893</t>
+          <t>55892</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89508</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106122</t>
+          <t>105215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>23051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28210</t>
+          <t>28506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44627</t>
+          <t>44758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38911</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51326</t>
+          <t>51403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>44851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>56071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87973</t>
+          <t>87842</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104390</t>
+          <t>104094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28865</t>
+          <t>28006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>33619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51464</t>
+          <t>51031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39508</t>
+          <t>39346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51129</t>
+          <t>51381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>45510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57737</t>
+          <t>58093</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88105</t>
+          <t>88538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106384</t>
+          <t>105950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18594</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>32249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31429</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40427</t>
+          <t>40691</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31865</t>
+          <t>31827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67270</t>
+          <t>66680</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80335</t>
+          <t>80527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34883</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25773</t>
+          <t>26276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41284</t>
+          <t>41506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50474</t>
+          <t>50972</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72090</t>
+          <t>71727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75763</t>
+          <t>76223</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>90616</t>
+          <t>91538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>69502</t>
+          <t>69280</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>85013</t>
+          <t>84510</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>149343</t>
+          <t>149706</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>170959</t>
+          <t>170461</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27820</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>43426</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28315</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60951</t>
+          <t>61024</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81492</t>
+          <t>82255</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47439</t>
+          <t>46741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62347</t>
+          <t>62033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52864</t>
+          <t>53766</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68262</t>
+          <t>68407</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105253</t>
+          <t>104490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>125794</t>
+          <t>125721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>141510</t>
+          <t>143346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>176257</t>
+          <t>175521</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>141508</t>
+          <t>145465</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>176911</t>
+          <t>180130</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>294665</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>343019</t>
+          <t>343331</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>327102</t>
+          <t>327838</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>361849</t>
+          <t>360013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>351638</t>
+          <t>348419</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>387041</t>
+          <t>383084</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>688889</t>
+          <t>688577</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>737243</t>
+          <t>736872</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>35639</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50439</t>
+          <t>50890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59418</t>
+          <t>59722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44788</t>
+          <t>44980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40978</t>
+          <t>40955</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51308</t>
+          <t>51088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78864</t>
+          <t>79498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93369</t>
+          <t>93708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>33774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35829</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45956</t>
+          <t>46298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>39168</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49621</t>
+          <t>49823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78729</t>
+          <t>79190</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93627</t>
+          <t>93729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16884</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19020</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33918</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45884</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49391</t>
+          <t>50088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54838</t>
+          <t>54840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98292</t>
+          <t>98446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103927</t>
+          <t>103946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>19488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>23999</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32670</t>
+          <t>32820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>40390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26819</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36481</t>
+          <t>36760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34464</t>
+          <t>34462</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43901</t>
+          <t>43726</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64659</t>
+          <t>65005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78545</t>
+          <t>78271</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15069</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>15804</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29416</t>
+          <t>29070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79901</t>
+          <t>79954</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95238</t>
+          <t>95179</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85103</t>
+          <t>86500</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100219</t>
+          <t>101308</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>170868</t>
+          <t>170400</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>192722</t>
+          <t>191439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,27%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36803</t>
+          <t>36750</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>20469</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>35277</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45758</t>
+          <t>47041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>68080</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99184</t>
+          <t>99072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109172</t>
+          <t>109273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109773</t>
+          <t>108692</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>121478</t>
+          <t>120835</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211971</t>
+          <t>212024</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>228047</t>
+          <t>227889</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16355</t>
+          <t>16467</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33406</t>
+          <t>33353</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>379315</t>
+          <t>380002</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>407294</t>
+          <t>407906</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>433225</t>
+          <t>436171</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>461879</t>
+          <t>462974</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>824703</t>
+          <t>822566</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>862665</t>
+          <t>861399</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>69671</t>
+          <t>69059</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>96963</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76272</t>
+          <t>75177</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104926</t>
+          <t>101980</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>152450</t>
+          <t>153716</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>190412</t>
+          <t>192549</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22448</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32923</t>
+          <t>33397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34608</t>
+          <t>34490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44789</t>
+          <t>44481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60521</t>
+          <t>60226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75007</t>
+          <t>74554</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>21946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36383</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31220</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>36119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>43348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62153</t>
+          <t>62433</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38216</t>
+          <t>39248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51939</t>
+          <t>51739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>38738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51760</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82140</t>
+          <t>81860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101252</t>
+          <t>100945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>18075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30373</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17698</t>
+          <t>18430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30686</t>
+          <t>31179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>40743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58135</t>
+          <t>58059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37378</t>
+          <t>37780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>32923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46404</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61823</t>
+          <t>61899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79486</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,04%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28698</t>
+          <t>28296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>37935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>31684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41471</t>
+          <t>41486</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63643</t>
+          <t>63259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76999</t>
+          <t>77366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14915</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15074</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28430</t>
+          <t>28814</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29260</t>
+          <t>28932</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32412</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63504</t>
+          <t>62953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19265</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34301</t>
+          <t>34376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46030</t>
+          <t>46312</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>23517</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60777</t>
+          <t>60412</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76942</t>
+          <t>77042</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>63879</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81368</t>
+          <t>80337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127986</t>
+          <t>128681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152138</t>
+          <t>152188</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>35105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51370</t>
+          <t>51735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>37385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53189</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>77731</t>
+          <t>77681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101883</t>
+          <t>101188</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120127</t>
+          <t>119453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127191</t>
+          <t>127179</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>123477</t>
+          <t>122903</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>133690</t>
+          <t>133196</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246524</t>
+          <t>246704</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>258722</t>
+          <t>259139</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22352</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>332904</t>
+          <t>334612</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>368716</t>
+          <t>370677</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>372009</t>
+          <t>373103</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>409489</t>
+          <t>409824</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>717982</t>
+          <t>718387</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>767086</t>
+          <t>767403</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>147309</t>
+          <t>145348</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>183121</t>
+          <t>181413</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>152242</t>
+          <t>151907</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>189722</t>
+          <t>188628</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>310353</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>359774</t>
+          <t>359369</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>28284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40512</t>
+          <t>40342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41291</t>
+          <t>44998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>66420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66883</t>
+          <t>67053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75750</t>
+          <t>75518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112136</t>
+          <t>112306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139744</t>
+          <t>138994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26920</t>
+          <t>26491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36614</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>29880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57897</t>
+          <t>59166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98728</t>
+          <t>99157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117516</t>
+          <t>116854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89561</t>
+          <t>88314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107225</t>
+          <t>107657</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193926</t>
+          <t>192657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221695</t>
+          <t>221943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>27906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43170</t>
+          <t>43096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51915</t>
+          <t>51714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51119</t>
+          <t>50018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59915</t>
+          <t>59843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97190</t>
+          <t>96936</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109479</t>
+          <t>110008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31233</t>
+          <t>31976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27885</t>
+          <t>28474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54572</t>
+          <t>53982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>51360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82589</t>
+          <t>83557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>53183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22984</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>49082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65110</t>
+          <t>64142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97863</t>
+          <t>96339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28431</t>
+          <t>28728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>21699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29232</t>
+          <t>29171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>21513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31916</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46801</t>
+          <t>46504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29715</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31039</t>
+          <t>31213</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46230</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>26494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>36031</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>27515</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38575</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56123</t>
+          <t>56499</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71314</t>
+          <t>71140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109049</t>
+          <t>109674</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118875</t>
+          <t>119587</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136146</t>
+          <t>136777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>149902</t>
+          <t>149620</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>250049</t>
+          <t>250092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>266611</t>
+          <t>266173</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97562</t>
+          <t>97323</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>114075</t>
+          <t>113982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>117416</t>
+          <t>116941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135090</t>
+          <t>135201</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>219482</t>
+          <t>220382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>243749</t>
+          <t>244777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>17637</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34057</t>
+          <t>34296</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21047</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>39196</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44008</t>
+          <t>42980</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68275</t>
+          <t>67375</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>174745</t>
+          <t>176846</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>229342</t>
+          <t>228486</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>236671</t>
+          <t>234238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>291279</t>
+          <t>289888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>428080</t>
+          <t>426337</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>505781</t>
+          <t>506888</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>434217</t>
+          <t>435073</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>488814</t>
+          <t>486713</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>468036</t>
+          <t>469427</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>522644</t>
+          <t>525077</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>917093</t>
+          <t>915986</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>994794</t>
+          <t>996537</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,04%</t>
         </is>
       </c>
     </row>
